--- a/gst_recon/sample_data/tally_purchase_register_2025-03.xlsx
+++ b/gst_recon/sample_data/tally_purchase_register_2025-03.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,11 @@
       <c r="P5" s="1" t="inlineStr">
         <is>
           <t>Input IGST 12%</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>Narration</t>
         </is>
       </c>
     </row>
